--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_05_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_05_18_Cau.xlsx
@@ -608,7 +608,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -622,7 +626,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Age bắt đầu ở source/effective time.</t>
+          <t>Độ tuổi của dữ liệu (data age) mà consumer quan sát được theo watermark: Tính từ mốc thời gian watermark an toàn (14:40) đến thời điểm hiện tại của hệ thống (15:10): 15:10 - 14:40 = 30 phút.</t>
         </is>
       </c>
     </row>
@@ -752,7 +756,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn signal có thể phản ánh parser làm rỗng/cắt/đổi language.</t>
+          <t>Khi số lượng dòng vẫn ổn định nhưng chất lượng câu trả lời bị suy giảm sau khi cập nhật bộ phân tích cú pháp (parser), các tín hiệu hữu ích để phát hiện sự cố dữ liệu gồm: (a) Tỷ lệ giá trị null theo từng trường dữ liệu; (b) Phân phối độ dài văn bản (text-length distribution) phát hiện hiện tượng bị cắt cụt; (c) Tỷ lệ phối hợp ngôn ngữ (language mix) phát hiện lỗi dịch/nhầm locale; (d) Số lượng giá trị phân biệt và độ hỗn loạn thông tin (cardinality/entropy) phát hiện lỗi trùng lặp/giảm đa dạng.</t>
         </is>
       </c>
     </row>
@@ -914,7 +918,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bắt đầu ở thứ agent nhìn thấy rồi lần producer của từng artifact.</t>
+          <t>Trình tự truy vết nguồn gốc dữ liệu ngược dòng (backwards data lineage) từ kết quả phục vụ agent về nguồn dữ liệu gốc: 1. Retrieved chunk mà agent trực tiếp quan sát thấy trong context (o5) -&gt; 2. Active index snapshot đang phục vụ truy vấn tại thời điểm đó (o2) -&gt; 3. Bản ghi chuẩn hóa (canonical record) trong kho lưu trữ (o4) -&gt; 4. Tác vụ và artifact chuyển đổi (transform run/artifact) tạo ra bản ghi đó (o1) -&gt; 5. Định danh và phiên bản dữ liệu nguồn ban đầu (source identity/version) (o3).</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1037,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi khi breach thì ai biết, ai làm gì và learner thấy gì.</t>
+          <t>Một thỏa thuận mức dịch vụ về độ tươi mới dữ liệu (freshness SLA) có tính hành động cao bắt buộc phải có: (a) Thời điểm phát sinh sự kiện kinh doanh tại nguồn để bắt đầu tính thời gian; (b) Ranh giới xuất bản dữ liệu phục vụ agent để kết thúc tính thời gian; (c) Ngưỡng thời gian và quy trình cảnh báo/leo thang khi vi phạm; (d) Người chịu trách nhiệm cụ thể và quy định hành vi xử lý khi dữ liệu bị cũ/quá hạn (stale-data policy).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_05_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_05_18_Cau.xlsx
@@ -657,10 +657,22 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính delta giữa từng cặp stage, không chỉ source và publish.
-Phân tích theo nguyên lý thiết kế: Tính delta giữa từng cặp stage, không chỉ source và publish.</t>
+- [1.5 điểm] Tính toán chính xác delta qua từng stage và định vị chính xác vị trí sụt giảm đột biến là Ingest -&gt; Clean (mất 2.080 dòng, ~20.4%).
+- [1.5 điểm] Nhận diện việc 2.080 dòng biến mất mà không vào Quarantine (chỉ có 50 dòng) là lỗi lọc âm thầm (silent drop).
+- [1.0 điểm] Nêu rõ các bằng chứng cụ thể cần kiểm tra tiếp: filter logs, inner join conditions và phân tích diff giữa hai tập dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định vị trí sụt giảm số lượng và Định lượng (Quantification):
+   - Stage 1 (Source -&gt; Ingest): 10.200 -&gt; 10.180 (Sụt giảm 20 dòng, tương đương 0.20% - hao hụt mạng/batch boundary bình thường).
+   - Stage 2 (Ingest -&gt; Clean): 10.180 -&gt; 8.100 (SỤT GIẢM ĐỘT BIẾN: MẤT 2.080 DÒNG, tương đương giảm 20.43%). Đây là vị trí sụt giảm số lượng bất thường lớn nhất trong toàn bộ đường ống.
+   - Stage 3 (Clean -&gt; Publish vs Quarantine): 8.100 bản ghi sau clean, trong đó 50 dòng vào Quarantine và 8.050 dòng được Publish (8.050 + 50 = 8.100 -&gt; Hoàn toàn khớp số học 100%).
+   - Tổng kết: Điểm rơi rụng dữ liệu nghiêm trọng nằm tại Bước Chuyển Ingest -&gt; Clean (thất thoát 2.080 bản ghi).
+2. Evidence cần xem tiếp để điều tra:
+   - Filter / Drop Log của cleaning pipeline: Kiểm tra các câu lệnh `WHERE`, regex filter hoặc inner join trong mã nguồn làm sạch để xem rule nào đã loại bỏ 2.080 dòng này mà không đưa vào Quarantine;
+   - Phân tích phân phối của 2.080 dòng bị mất: Đối chiếu diff giữa Ingest dataset và Clean dataset xem các dòng bị mất có chung thuộc tính nào (ví dụ: null trường tùy chọn, sai định dạng ngày, hoặc lỗi parse encoding).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quan sát dung lượng dữ liệu (Data Volume Observability) phải được thực hiện bằng cách đo đếm Delta (chênh lệch) giữa từng cặp công đoạn liên tiếp (Stage-to-Stage Volume Accounting). Khi một stage làm mất một lượng lớn dữ liệu (hơn 20%) mà số lượng đó không xuất hiện trong bảng cách ly (Quarantine table chỉ có 50 dòng), đây là dấu hiệu của một 'Silent Filter Drop' (bị lọc âm thầm do code lỗi) vi phạm nguyên tắc bảo toàn dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Monte Carlo - Volume Anomaly Detection in Data Pipelines: https://www.montecarlodata.com/ và Google Cloud Data Loss Prevention Standards</t>
         </is>
       </c>
     </row>
@@ -787,10 +799,23 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mô tả cái đã đổi trước khi đoán tại sao.
-Phân tích theo nguyên lý thiết kế: Mô tả cái đã đổi trước khi đoán tại sao.</t>
+- [1.5 điểm] Diễn giải chính xác và khách quan các thay đổi phân phối: sụt giảm 91% độ dài văn bản trung vị và tăng vọt nhãn ngôn ngữ không xác định lên 55%.
+- [1.5 điểm] Lựa chọn hành động an toàn: tạm dừng xuất bản vào vector search và trích xuất mẫu đại diện để kiểm tra trực quan (visual inspection).
+- [1.0 điểm] Thể hiện tư duy khoa học, tránh phỏng đoán kết luận quá mức khi chưa có đủ bằng chứng từ việc rà soát mẫu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Diễn giải sự thay đổi phân phối dữ liệu (Distribution Shift):
+   - Độ dài văn bản: Trung vị sụt giảm nghiêm trọng từ 800 ký tự xuống còn 70 ký tự (giảm hơn 91% độ dài, văn bản bị ngắn bất thường).
+   - Tỷ lệ Null: Tăng nhẹ từ 1% lên 2% (trong giới hạn biến động nhỏ).
+   - Phân bố ngôn ngữ: Tỷ lệ tiếng Việt sụt giảm mạnh từ 95% xuống 40%, trong khi tỷ lệ 'không rõ ngôn ngữ' (unknown language) tăng vọt từ ~4% lên 55%.
+   - Kết luận hiện tượng: Dữ liệu văn bản đầu vào đang bị cụt lủn (truncated) hoặc bị lỗi giải mã/OCR khiến bộ phân loại ngôn ngữ không nhận diện được tiếng Việt, dẫn đến bị gán nhãn unknown.
+2. Lựa chọn hành động thận trọng (Action without Overreaching):
+   - Hành động 1 (Tạm đình chỉ xuất bản): Chặn việc đưa batch dữ liệu này vào pipeline tạo embedding cho Vector Database của RAG Agent để ngăn ô nhiễm kiến thức.
+   - Hành động 2 (Lấy mẫu điều tra thực tế): Trích xuất ngẫu nhiên 50 bản ghi thuộc nhóm 'unknown language, median length 70' để kiểm tra trực quan: xem tài liệu bị cắt cụt do parser hay do văn bản bị lỗi font (mojibake) hay do nguồn cung cấp thay đổi loại tài liệu.
+   - Tuyệt đối không vội vàng phỏng đoán nguyên nhân hoặc tự ý sửa đổi tham số mô hình phân loại ngôn ngữ khi chưa có bằng chứng thực tế.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quan sát phân phối dữ liệu (Data Distribution Observability) yêu cầu kỹ sư tuân thủ kỷ luật 'Mô tả chính xác điều đã thay đổi trước khi đưa ra giả thuyết tại sao'. Sự sụt giảm đồng thời của độ dài văn bản và sự gia tăng nhãn không rõ ngôn ngữ là triệu chứng điển hình của lỗi tiền xử lý (preprocessing/parsing corruption). Việc đình chỉ xuất bản và lấy mẫu điều tra thực nghiệm là hành động chuẩn mực để kiểm soát rủi ro mà không can thiệp vội vàng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Evidently AI - Data Drift and Distribution Monitoring: https://docs.evidentlyai.com/ và Google SRE Book - Monitoring Data Pipelines</t>
         </is>
       </c>
     </row>
@@ -821,10 +846,24 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đánh giá từng field đối với consumer cụ thể.
-Phân tích theo nguyên lý thiết kế: Đánh giá từng field đối với consumer cụ thể.</t>
+- [1.5 điểm] Phân loại chính xác các thay đổi: amount đổi sang string là breaking change nguy hiểm; currency là non-breaking change.
+- [1.5 điểm] Phân tích cụ thể hậu quả đối với consumer thực hiện phép cộng số: crash TypeError hoặc tính sai do nối chuỗi ký tự.
+- [1.0 điểm] Đưa ra giải pháp khắc phục an toàn: chặn schema v2 trực tiếp, cung cấp trường tương thích ngược hoặc an toàn ép kiểu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại các thay đổi trong Schema:
+   - `customer_id: str`: Giữ nguyên, hoàn toàn tương thích (Compatible).
+   - `amount: int` -&gt; `amount: string`: ĐÂY LÀ BREAKING CHANGE (Phá vỡ tính tương thích ngược). Kiểu dữ liệu bị đổi từ số nguyên sang chuỗi ký tự.
+   - `currency?: str`: NON-BREAKING CHANGE (Thay đổi tương thích ngược). Bổ sung trường tùy chọn (optional field) mới.
+2. Consumer bị ảnh hưởng:
+   - Consumer thực hiện phép tính 'cộng amount như số' (Aggregation / Financial Consumer) sẽ bị CRASH ngay lập tức với lỗi kiểu dữ liệu (TypeError: unsupported operand type for +: 'str') hoặc tệ hơn là thực hiện phép nối chuỗi ('10' + '20' = '1020' thay vì 30), dẫn đến sai lệch số liệu tài chính nghiêm trọng.
+3. Hành động cần làm ngay:
+   - Chặn xuất bản phiên bản Schema v2 dạng string trực tiếp ra kênh chung;
+   - Nếu cần lưu trữ số lớn hoặc định dạng tiền tệ, triển khai tương thích ngược: Duy trì `amount_numeric: int` cho consumer cũ và cung cấp `amount_str: str` hoặc tạo Database View tự động cast chuỗi về số;
+   - Cập nhật Consumer Code với cơ chế phòng vệ: ép kiểu an toàn `safe_cast_int(row['amount'])` kèm kiểm tra ngoại lệ trước khi tính toán.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thay đổi kiểu dữ liệu của một trường hiện có từ kiểu số sang chuỗi là một trong những vi phạm tương thích schema (Schema Compatibility Violation) nghiêm trọng nhất. Các consumer dựa vào hợp đồng kiểu số sẽ bị đổ vỡ hoặc tạo ra lỗi sai số học tiềm ẩn (silent mathematical corruption). Quản trị Schema bắt buộc phải sử dụng công cụ như Confluent Schema Registry với chế độ BACKWARD compatibility để tự động chặn các thay đổi phá vỡ này.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Confluent Schema Registry - Schema Evolution and Compatibility: https://docs.confluent.io/platform/current/schema-registry/fundamentals/schema-evolution.html và Apache Avro Specification</t>
         </is>
       </c>
     </row>
@@ -949,10 +988,23 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Dừng đúng chỗ identity chain bị đứt.
-Phân tích theo nguyên lý thiết kế: Dừng đúng chỗ identity chain bị đứt.</t>
+- [1.5 điểm] Dựng lại đầy đủ và chuẩn xác các mắt xích đã biết trong chuỗi lineage: C7 -&gt; I3 -&gt; K9 và ghi nhận sự tồn tại của S2 v1/v2.
+- [1.5 điểm] Chỉ ra chính xác điểm đứt gãy đầu tiên nằm tại K9 do thiếu run_id / source provenance trỏ về S2.
+- [1.0 điểm] Phân tích sâu sắc tác động: mất khả năng truy vết nguồn gốc khi có sự cố và không thể replay đơn định.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Dựng lại chuỗi Lineage đã biết:
+   - `Chunk C7` thuộc về `Index I3` (Retrieval Layer);
+   - `Index I3` có manifest trỏ trực tiếp đến `Canonical dataset K9` (Canonical Layer);
+   - Nguồn gốc ban đầu là `Source S2` (Source Layer), nhưng S2 lại có hai phiên bản khác nhau (v1 và v2).
+2. Điểm đứt gãy Lineage đầu tiên (First Broken Link):
+   - Điểm đứt nằm tại: Liên kết giữa `Canonical K9` và `Source S2`. Nguyên nhân là `K9 thiếu run_id` (và thiếu source_snapshot_id / commit_hash). Khi không có run_id, hoàn toàn không thể xác định K9 được tạo ra từ lần chạy nào, vào thời điểm nào, và bắt nguồn từ phiên bản nào của S2 (S2 v1 hay S2 v2).
+3. Tác động của điểm đứt gãy (Impact):
+   - Mất tính bất biến và khả năng truy vết (Traceability Loss): Khi Chunk C7 bị người dùng khiếu nại là sai lệch, đội ngũ kỹ thuật không thể xác định thông tin đó xuất phát từ phiên bản nào của nguồn S2;
+   - Bất khả thi trong việc tái lập (Replayability Failure): Không thể chạy lại pipeline một cách tin cậy để sửa lỗi vì không biết đầu vào chính xác của K9 là gì.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chuỗi định danh nguồn gốc dữ liệu (Data Lineage Chain) đòi hỏi tính liên tục không đứt đoạn từ Source -&gt; Ingestion Run -&gt; Canonical -&gt; Index -&gt; Chunk. Một khi bất kỳ mắt xích nào bị thiếu thuộc tính neo đậu ngữ cảnh (contextual anchor như `run_id` hay `source_version_hash`), toàn bộ tính khả tín của chuỗi truy vết phía sau sẽ sụp đổ. Dừng lại đúng điểm đứt gãy cho phép khoanh vùng chính xác nơi cần bổ sung metadata quản trị.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenLineage Specification - Lineage Metadata &amp; Job Run Context: https://openlineage.io/ và W3C PROV-DM: The PROV Data Model: https://www.w3.org/TR/prov-dm/</t>
         </is>
       </c>
     </row>
@@ -983,10 +1035,29 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi clock bắt đầu ở business event và dừng nơi agent nhìn thấy.
-Phân tích theo nguyên lý thiết kế: Mỗi clock bắt đầu ở business event và dừng nơi agent nhìn thấy.</t>
+- [1.5 điểm] Thiết kế chi tiết 2 đồng hồ đo độ tươi với điểm bắt đầu (business event) và điểm kết thúc (agent readable) cùng ngưỡng SLA chuẩn (2 phút cho ticket, 24 giờ cho PDF).
+- [1.5 điểm] Phân định owner tiếp nhận cảnh báo cụ thể cho từng loại pipeline tương ứng.
+- [1.0 điểm] Quy định rõ ràng hành vi phản ứng của Agent khi dữ liệu bị stale (cảnh báo người dùng, hạ cấp dịch vụ an toàn).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Hai Đồng Hồ Đo Độ Tươi (Two Freshness Clocks):
+   - Đồng hồ 1 (Live Ticket Status Clock - 2 phút SLA):
+     + Điểm bắt đầu (T0): Thời điểm sự kiện trạng thái ticket phát sinh tại hệ thống nguồn (Event Timestamp `ticket.status_changed_at`).
+     + Điểm kết thúc (T1): Thời điểm dữ liệu cập nhật có mặt trong in-memory cache/database mà Agent đọc trực tiếp.
+     + Độ trễ = `T1 - T0`. Ngưỡng cảnh báo: Cảnh báo mềm khi &gt; 90 giây; Báo động vi phạm SLA khi &gt; 120 giây (2 phút).
+   - Đồng hồ 2 (Policy PDF Document Clock - 24 giờ SLA):
+     + Điểm bắt đầu (T0): Thời điểm file policy PDF mới được upload hoặc phê duyệt trên cổng HR/Legal (`policy.effective_or_published_at`).
+     + Điểm kết thúc (T1): Thời điểm file hoàn tất parse, chunk, embed và Vector Index Alias chuyển sang phục vụ chunk mới.
+     + Độ trễ = `T1 - T0`. Ngưỡng cảnh báo: Cảnh báo sau 18 giờ; Vi phạm SLA sau 24 giờ.
+2. Owner nhận Alert:
+   - Luồng Ticket: Realtime Streaming On-Call / Customer Support Platform Team.
+   - Luồng Policy PDF: Knowledge Base &amp; RAG Indexing Pipeline Owner.
+3. Hành vi khi dữ liệu bị cũ (Stale Data Behavior):
+   - Đối với Ticket: Agent từ chối khẳng định tuyệt đối, phản hồi kèm cảnh báo minh bạch: 'Dữ liệu trạng thái đang cập nhật chậm hơn bình thường, vui lòng kiểm tra trực tiếp trên portal...';
+   - Đối với Policy: Khi clock vượt 24h mà chưa index bản mới, hệ thống kích hoạt fallback cảnh báo RAG Agent ghi chú nguồn tài liệu đang chờ kiểm duyệt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thiết kế SLA độ tươi (Freshness SLA Design) cho hệ thống AI Agent phải phản ánh đúng kỳ vọng nghiệp vụ của từng loại dữ liệu: dữ liệu tác nghiệp thời gian thực (Ticket) đòi hỏi phản ứng theo giây, trong khi dữ liệu tri thức tĩnh/bán tĩnh (Policy) vận hành theo chu kỳ ngày. Mỗi đồng hồ phải đo lường trọn vẹn từ lúc sự việc xảy ra ở thế giới thực đến lúc Agent có thể tiếp cận được, kèm theo hành vi phòng vệ chủ động (Graceful Degradation) khi dữ liệu rơi vào trạng thái stale.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Workbook - Alerting on SLOs: https://sre.google/workbook/alerting-on-slos/ và Principles of Chaos Engineering - Graceful Degradation</t>
         </is>
       </c>
     </row>
@@ -1113,10 +1184,23 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm window trước, rồi tìm signal độc lập cùng đổi.
-Phân tích theo nguyên lý thiết kế: Kiểm window trước, rồi tìm signal độc lập cùng đổi.</t>
+- [1.5 điểm] Đánh giá sâu sắc sự chênh lệch quy mô cửa sổ dữ liệu (1 ngày vs 30 ngày) và ý nghĩa của KL Divergence.
+- [1.5 điểm] Phân tích mối tương quan đồng quy giữa 3 tín hiệu độc lập: KL drift ngôn ngữ, lỗi OCR tăng và grounding rate của RAG sụt giảm.
+- [1.0 điểm] Đưa ra hành động dứt khoát: chặn nạp dữ liệu, khoanh vùng lỗi ở tầng OCR và bảo vệ chất lượng câu trả lời của agent.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Diễn giải phương pháp và cửa sổ dữ liệu (Window &amp; Method Assessment):
+   - Cửa sổ dữ liệu bị lệch quy mô nghiêm trọng: Mốc tham chiếu (baseline window) là 30 ngày (tập dữ liệu lớn, độ ổn định cao), trong khi dữ liệu hiện tại chỉ là 1 ngày (mẫu nhỏ, dễ bị ảnh hưởng bởi biến động ngẫu nhiên - sample variance).
+   - Chỉ số khoảng cách phân phối: Độ phân kỳ KL Divergence cao ở trường ngôn ngữ chỉ ra sự sai khác phân phối xác suất rất lớn giữa hai tập.
+2. Đánh giá tín hiệu độc lập cùng thay đổi (Multi-Signal Correlation):
+   - Không thể coi đây chỉ là biến động ngẫu nhiên trong 1 ngày, bởi vì có hai tín hiệu đo lường độc lập khác CÙNG THAY ĐỔI THEO CHIỀU HƯỚNG XẤU: (a) Tỷ lệ OCR không rõ ngôn ngữ tăng vọt; (b) Grounding rate của Agent sụt giảm mạnh. Sự hội tụ của 3 tín hiệu độc lập này xác nhận hệ thống đang gặp sự cố thực tế nghiêm trọng ở khâu xử lý OCR/tiền xử lý.
+3. Lựa chọn hành động:
+   - Lập tức chặn việc tự động nạp dữ liệu của ngày hôm đó vào Vector Store;
+   - Kiểm tra lại các file PDF và phiên bản OCR model vừa được triển khai trong ngày để tìm nguyên nhân sinh ra văn bản rác;
+   - Rollback hoặc cách ly các chunk lỗi và đánh giá lại grounding rate sau khi sửa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi phân tích độ lệch phân phối (Distribution Drift), nếu chỉ nhìn vào một chỉ số thống kê (như KL Divergence) trên một cửa sổ thời gian ngắn (1 ngày vs 30 ngày), người ta dễ hoài nghi về hiện tượng nhiễu mẫu. Tuy nhiên, nguyên lý 'Đồng quy tín hiệu' (Signal Convergence) chỉ ra rằng: nếu nhiều chỉ số đo lường độc lập từ các tầng khác nhau (Data layer: OCR confidence/language drift; Application layer: RAG grounding rate) cùng đồng thời báo suy thoái, thì đó chắc chắn là một sự cố hệ thống có thật đòi hỏi can thiệp khẩn cấp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Evidently AI - Drift Detection Methods (KL Divergence, PSI) &amp; Multimodal Evaluation: https://docs.evidentlyai.com/ và Arize Phoenix - LLM Groundedness and Retrieval Evaluation</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1280,22 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ evaluation set cố định và tách impact khỏi root cause.
-Phân tích theo nguyên lý thiết kế: Giữ evaluation set cố định và tách impact khỏi root cause.</t>
+- [1.5 điểm] Xây dựng chuỗi liên kết nhân quả chặt chẽ qua 4 tầng: Parser release -&gt; null-text (+20%) -&gt; hit@5 (0.82 -&gt; 0.60) -&gt; grounded rate (0.78 -&gt; 0.55).
+- [1.5 điểm] Nhấn mạnh vai trò của việc giữ cố định tập đánh giá 100 queries để bảo đảm tính khoa học của phép đo lường.
+- [1.0 điểm] Đưa ra kết luận có căn cứ rõ ràng và biện pháp xử lý dứt khoát (rollback parser và re-index).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Nối chuỗi Evidence nhân quả (Causal Evidence Chain):
+   - Sự kiện ban đầu: Triển khai phát hành phiên bản mới của bộ phân tích cú pháp (Parser Release).
+   - Bằng chứng tầng Dữ liệu (Data Pipeline Metric): Tỷ lệ chuỗi văn bản rỗng/null (`null-text`) tăng vọt thêm 20% trong kho tri thức.
+   - Bằng chứng tầng Truy hồi (Retrieval Metric): Trên cùng tập kiểm định chuẩn 100 câu truy vấn (fixed evaluation benchmark), độ chính xác tìm kiếm `hit@5` sụt giảm nghiêm trọng từ 0.82 xuống 0.60 (giảm 22%).
+   - Bằng chứng tầng Ứng dụng (Agent Metric): Tỷ lệ câu trả lời có căn cứ tài liệu (`grounded-answer rate`) sụt giảm tương ứng từ 0.78 xuống 0.55 (giảm 23%).
+2. Phát biểu kết luận đúng mức (Calibrated Conclusion):
+   - 'Có bằng chứng thực nghiệm mạnh mẽ và nhất quán chứng minh rằng: Việc triển khai parser mới đã trực tiếp làm gia tăng 20% văn bản null trong pipeline dữ liệu, dẫn đến sự suy giảm nghiêm trọng chất lượng truy hồi (hit@5 giảm 22 điểm %), từ đó là nguyên nhân trực tiếp kéo tụt tỷ lệ câu trả lời có căn cứ của Agent xuống 23 điểm % trên tập benchmark 100 queries.'
+   - Hành động: Lập tức rollback parser về phiên bản trước đó và re-index lại kho dữ liệu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Để chứng minh mối liên kết nhân quả giữa khuyết tật dữ liệu và Service Level Indicator (SLI) của Agent, việc duy trì một tập kiểm thử cố định (Fixed Evaluation Benchmark - 100 queries) là điều kiện tiên quyết nhằm loại bỏ yếu tố biến động từ người dùng. Chuỗi bằng chứng phải thể hiện rõ tính lan truyền từ: Code Change -&gt; Data Quality Failure (null-text) -&gt; Retrieval Failure (hit@5) -&gt; Agent Performance Degradation (groundedness).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RAGAS: Automated Evaluation of Retrieval Augmented Generation: https://docs.ragas.io/ và Google SRE Book - Linking System Metrics to User Experience</t>
         </is>
       </c>
     </row>
@@ -1230,10 +1326,20 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đặt ở điểm sớm nhất check có đủ fields để quyết.
-Phân tích theo nguyên lý thiết kế: Đặt ở điểm sớm nhất check có đủ fields để quyết.</t>
+- [1.5 điểm] Bố trí chính xác vị trí Gate 1 (Required-ID) ngay sau bước clean và trước bước embed, giải thích rõ nguyên lý tiết kiệm compute.
+- [1.5 điểm] Xác định đúng vị trí và tính chất của Gate 2 (Optional-note) là Soft Warning Gate không cản trở retrieval.
+- [1.0 điểm] Thiết kế đầy đủ các nhánh xử lý khi fail: cô lập vào Quarantine/DLQ cho Hard Gate và ghi log cảnh báo cho Soft Gate.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Bố trí vị trí các Quality Gate trong DAG (`parse -&gt; clean -&gt; embed -&gt; publish`):
+   - Gate 1: 'Required-ID Schema Gate' (Hard Gate) -&gt; Đặt NGAY SAU BƯỚC CLEAN (trước khi vào bước embed: `parse -&gt; clean -&gt; [GATE 1] -&gt; embed`). Lý do: Đây là điểm sớm nhất trong DAG mà toàn bộ các trường canonical đã được hoàn tất chuẩn hóa. Đặt gate tại đây ngăn chặn hoàn toàn việc tiêu tốn chi phí compute đắt đỏ của GPU/Embedding API cho các bản ghi thiếu ID hợp lệ.
+   - Gate 2: 'Optional-Note Format Gate' (Soft Warning Gate) -&gt; Đặt song song hoặc sau bước clean. Vì trường ghi chú tùy chọn không ảnh hưởng đến khả năng retrieval của vector search, gate này chỉ đóng vai trò audit.
+2. Xác định các nhánh rẽ khi thất bại (Failure Branches):
+   - Khi Gate 1 thất bại (Missing Required ID): Nhánh chuyển hướng lập tức: Tách bản ghi vi phạm đẩy vào `Quarantine / Dead Letter Queue` kèm nguyên nhân lỗi; KHÔNG cho phép đi tiếp vào nhánh `embed`. Nhánh chính tiếp tục xử lý các bản ghi hợp lệ còn lại.
+   - Khi Gate 2 cảnh báo (Optional Note Issue): Bản ghi VẪN ĐƯỢC PHÉP ĐI TIẾP vào nhánh `embed -&gt; publish`, đồng thời ghi một log sự kiện vào bảng `data_quality_warnings` để đội vận hành theo dõi mà không làm gián đoạn pipeline.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc 'Fail-Early / Shift-Left' trong thiết kế DAG dữ liệu quy định rằng: Một phép kiểm tra chất lượng phải được đặt tại điểm sớm nhất có thể mà ở đó các thuộc tính cần kiểm tra đã hội đủ điều kiện để ra quyết định. Việc ngăn chặn các bản ghi hỏng trước công đoạn embedding giúp tiết kiệm chi phí tính toán lớn và bảo vệ tính toàn vẹn của Vector Index. Đồng thời, cần phân biệt rạch ròi giữa Hard Gate (chặn và rẽ nhánh cách ly) và Soft Gate (cảnh báo nhưng cho qua).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Apache Airflow Documentation - Data Quality Gates &amp; Branching: https://airflow.apache.org/docs/apache-airflow/stable/core-concepts/dags.html và Great Expectations in Pipeline DAGs</t>
         </is>
       </c>
     </row>
